--- a/word-data/category.xlsx
+++ b/word-data/category.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -683,9 +683,29 @@
         <v>13</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>nba</v>
+      </c>
+      <c r="B15" t="str">
+        <v/>
+      </c>
+      <c r="C15" t="str">
+        <v>Knicks</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/word-data/category.xlsx
+++ b/word-data/category.xlsx
@@ -1,56 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Categories" sheetId="1" r:id="rId1"/>
-    <sheet name="Phrase Categories" sheetId="2" r:id="rId2"/>
+    <sheet name="Categories" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Phrase Categories" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Categories!$A$1:$F$14</definedName>
-  </definedNames>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,13 +43,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -400,375 +441,501 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Subcategories</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Cover Image Word</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Total Words</v>
-      </c>
-      <c r="E1" t="str">
-        <v>With Image</v>
-      </c>
-      <c r="F1" t="str">
-        <v>With Example</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Subcategories</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cover Image Word</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Total Words</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>With Image</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>With Example</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Action</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Verb</v>
-      </c>
-      <c r="C2" t="str">
-        <v>eat</v>
-      </c>
-      <c r="D2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Verb</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>eat</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>49</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>19</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Adjective</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Emotion, Quality, Sensation, Size</v>
-      </c>
-      <c r="C3" t="str">
-        <v>cheap</v>
-      </c>
-      <c r="D3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Adjective</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Emotion, Quality, Sensation, Size</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cheap</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>59</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>28</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Animal</v>
-      </c>
-      <c r="B4" t="str">
-        <v>Bird, Farm&amp;Pet, Wildlife</v>
-      </c>
-      <c r="C4" t="str">
-        <v>bird</v>
-      </c>
-      <c r="D4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Animal</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bird, Farm&amp;Pet, Wildlife</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bird</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>38</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>20</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>Color</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Color</v>
-      </c>
-      <c r="C5" t="str">
-        <v>pink</v>
-      </c>
-      <c r="D5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>Day</v>
-      </c>
-      <c r="B6" t="str">
-        <v>Time</v>
-      </c>
-      <c r="C6" t="str">
-        <v>monday</v>
-      </c>
-      <c r="D6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
         <v>7</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>Food</v>
-      </c>
-      <c r="B7" t="str">
-        <v>Carb, Drink, Fruit, Pantry, Protein, Sweet, Vegetable</v>
-      </c>
-      <c r="C7" t="str">
-        <v>cherry</v>
-      </c>
-      <c r="D7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Carb, Drink, Fruit, Pantry, Protein, Sweet, Vegetable</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cherry</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
         <v>69</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>44</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>44</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>Nature</v>
-      </c>
-      <c r="B8" t="str">
-        <v>Landscape, Plant, Weather&amp;Sky</v>
-      </c>
-      <c r="C8" t="str">
-        <v>wind</v>
-      </c>
-      <c r="D8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Nature</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Landscape, Plant, Weather&amp;Sky</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>wind</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>31</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>10</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>Number</v>
-      </c>
-      <c r="B9" t="str">
-        <v>Number</v>
-      </c>
-      <c r="C9" t="str">
-        <v>eight</v>
-      </c>
-      <c r="D9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>eight</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>11</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>11</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>Object</v>
-      </c>
-      <c r="B10" t="str">
-        <v>Fun, Furniture, Kitchen, Misc, Tech, Tool</v>
-      </c>
-      <c r="C10" t="str">
-        <v>trophy</v>
-      </c>
-      <c r="D10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Object</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fun, Furniture, Kitchen, Misc, Tech, Tool</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>trophy</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>75</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>46</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>54</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="str">
-        <v>People</v>
-      </c>
-      <c r="B11" t="str">
-        <v>Body, Clothing, Family, Job</v>
-      </c>
-      <c r="C11" t="str">
-        <v>sister</v>
-      </c>
-      <c r="D11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Body, Clothing, Family, Job</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>sister</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>56</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>26</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="str">
-        <v>Place</v>
-      </c>
-      <c r="B12" t="str">
-        <v>City, Country, Home, Landmark, Place, Structure</v>
-      </c>
-      <c r="C12" t="str">
-        <v>bank</v>
-      </c>
-      <c r="D12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Place</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>City, Country, Home, Landmark, Place, Structure</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bank</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>87</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>15</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>33</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>Time</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Time</v>
-      </c>
-      <c r="C13" t="str">
-        <v>today</v>
-      </c>
-      <c r="D13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>18</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>5</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Transport</v>
-      </c>
-      <c r="C14" t="str">
-        <v>taxi</v>
-      </c>
-      <c r="D14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>taxi</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>18</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>13</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="str">
-        <v>nba</v>
-      </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v>Knicks</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>NBA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Series 1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5</v>
+      </c>
+      <c r="F15" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F15"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col width="20.83203125" customWidth="1" min="1" max="1"/>
+    <col width="18.83203125" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>Category</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Cover Image Word</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cover Image Word</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>greeting</v>
-      </c>
-      <c r="B2" t="str">
-        <v>hand</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>greeting</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>response</v>
-      </c>
-      <c r="B3" t="str">
-        <v>talk</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>response</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>talk</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>life</v>
-      </c>
-      <c r="B4" t="str">
-        <v>coffee</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>life</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>coffee</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>feeling</v>
-      </c>
-      <c r="B5" t="str">
-        <v>happy</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>feeling</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>happy</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>social</v>
-      </c>
-      <c r="B6" t="str">
-        <v>friend</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>social</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>